--- a/countries/se/2026-2029.xlsx
+++ b/countries/se/2026-2029.xlsx
@@ -59593,13 +59593,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O411" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R411" t="n">
-        <v>1.074661249252585</v>
+        <v>1.065316368824301</v>
       </c>
       <c r="U411" t="inlineStr">
         <is>
@@ -65632,13 +65632,13 @@
         </is>
       </c>
       <c r="N453" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O453" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R453" t="n">
-        <v>1.252213977389968</v>
+        <v>1.242869096961685</v>
       </c>
       <c r="U453" t="inlineStr">
         <is>
@@ -67072,13 +67072,13 @@
         </is>
       </c>
       <c r="N463" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O463" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R463" t="n">
-        <v>1.046626607967735</v>
+        <v>1.037281727539451</v>
       </c>
       <c r="U463" t="inlineStr">
         <is>
@@ -68182,7 +68182,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51492</v>
+        <v>51489</v>
       </c>
     </row>
     <row r="16">

--- a/countries/se/2026-2029.xlsx
+++ b/countries/se/2026-2029.xlsx
@@ -54841,13 +54841,13 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O378" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="R378" t="n">
-        <v>3.672538008315355</v>
+        <v>3.663193127887072</v>
       </c>
       <c r="U378" t="inlineStr">
         <is>
@@ -61744,13 +61744,13 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O426" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R426" t="n">
-        <v>0.1868976085656669</v>
+        <v>0.1775527281373836</v>
       </c>
       <c r="U426" t="inlineStr">
         <is>
@@ -62320,13 +62320,13 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O430" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="R430" t="n">
-        <v>4.046333225446689</v>
+        <v>4.036988345018405</v>
       </c>
       <c r="U430" t="inlineStr">
         <is>
@@ -62896,13 +62896,13 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R434" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="U434" t="inlineStr">
         <is>
@@ -64192,13 +64192,13 @@
         </is>
       </c>
       <c r="N443" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O443" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R443" t="n">
-        <v>0.8316943581172178</v>
+        <v>0.8223494776889344</v>
       </c>
       <c r="U443" t="inlineStr">
         <is>
@@ -65056,13 +65056,13 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O449" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R449" t="n">
-        <v>1.373697422957652</v>
+        <v>1.364352542529369</v>
       </c>
       <c r="U449" t="inlineStr">
         <is>
@@ -65632,13 +65632,13 @@
         </is>
       </c>
       <c r="N453" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O453" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R453" t="n">
-        <v>1.242869096961685</v>
+        <v>1.233524216533401</v>
       </c>
       <c r="U453" t="inlineStr">
         <is>
@@ -68182,7 +68182,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51489</v>
+        <v>51482</v>
       </c>
     </row>
     <row r="16">
